--- a/Excel/Documentación/Clases/06- PrimerLibro.xlsx
+++ b/Excel/Documentación/Clases/06- PrimerLibro.xlsx
@@ -2,25 +2,37 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\Esquema del día\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{994F5A8F-DAE0-47C9-8DB7-F4B3D515CE4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10DB4826-90D3-4291-A8E5-9378FEBA6C49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23929" yWindow="-113" windowWidth="18257" windowHeight="10769" xr2:uid="{F33C70C0-13D4-4C74-BC8E-4229D5E1BE35}"/>
+    <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Contabilidad" sheetId="1" r:id="rId1"/>
     <sheet name="Ventas" sheetId="2" r:id="rId2"/>
+    <sheet name="01 Ordenado" sheetId="3" r:id="rId3"/>
+    <sheet name="02 Filtrado" sheetId="4" r:id="rId4"/>
+    <sheet name="03 Reemplazar" sheetId="5" r:id="rId5"/>
+    <sheet name="Filtro avanzado" sheetId="10" r:id="rId6"/>
+    <sheet name="Buscar y Reemplazar" sheetId="11" r:id="rId7"/>
+    <sheet name="Pruebas" sheetId="12" r:id="rId8"/>
+    <sheet name="Contabilidad (2)" sheetId="14" r:id="rId9"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Contabilidad (2)'!$A$1:$I$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Filtro avanzado'!$A$1:$I$11</definedName>
+    <definedName name="_xlnm.Extract" localSheetId="8">'Contabilidad (2)'!$A$16:$I$16</definedName>
+    <definedName name="_xlnm.Extract" localSheetId="5">'Filtro avanzado'!#REF!</definedName>
+    <definedName name="_xlnm.Criteria" localSheetId="8">'Contabilidad (2)'!$C$13:$E$14</definedName>
+    <definedName name="_xlnm.Criteria" localSheetId="5">'Filtro avanzado'!$A$14:$B$15</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -32,15 +44,70 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Nuria López Álvarez</author>
+  </authors>
+  <commentList>
+    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{446A3BDE-5BF0-4CB7-8E01-9C86CBD2627A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Nuria López Álvarez:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+patatín</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E9" authorId="0" shapeId="0" xr:uid="{43F33999-903E-4418-90C7-04E0FD7548DF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Nuria López Álvarez:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+patatán</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="49">
   <si>
     <t>ID</t>
   </si>
@@ -69,16 +136,37 @@
     <t>NOMBRE-SEXO</t>
   </si>
   <si>
+    <t>Alma Gutiérrez</t>
+  </si>
+  <si>
+    <t>Femenino</t>
+  </si>
+  <si>
+    <t>Finanzas</t>
+  </si>
+  <si>
+    <t>Israel Fonseca</t>
+  </si>
+  <si>
+    <t>Masculino</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>Miguel Ladrón</t>
+  </si>
+  <si>
+    <t>Relaciones Exteriores</t>
+  </si>
+  <si>
+    <t>Cecilia Jaca</t>
+  </si>
+  <si>
     <t>Alejandro Gómez</t>
   </si>
   <si>
-    <t>Alma Gutiérrez</t>
-  </si>
-  <si>
-    <t>Masculino</t>
-  </si>
-  <si>
-    <t>Femenino</t>
+    <t>Rosaura Yépez</t>
   </si>
   <si>
     <t>Alondra Gómez</t>
@@ -87,36 +175,15 @@
     <t>Argenee Alamo</t>
   </si>
   <si>
-    <t>Cecilia Jaca</t>
-  </si>
-  <si>
     <t>Gilberto Galardi</t>
   </si>
   <si>
-    <t>Israel Fonseca</t>
-  </si>
-  <si>
-    <t>Miguel Ladrón</t>
-  </si>
-  <si>
-    <t>Rosaura Yépez</t>
+    <t>Comercio</t>
   </si>
   <si>
     <t>Víctor Yépez</t>
   </si>
   <si>
-    <t>Relaciones Exteriores</t>
-  </si>
-  <si>
-    <t>Finanzas</t>
-  </si>
-  <si>
-    <t>Marketing</t>
-  </si>
-  <si>
-    <t>Comercio</t>
-  </si>
-  <si>
     <t>Recursos Humanos</t>
   </si>
   <si>
@@ -157,34 +224,129 @@
   </si>
   <si>
     <t>DICIEMBRE</t>
+  </si>
+  <si>
+    <t>3.8.4 · Orden personalizado</t>
+  </si>
+  <si>
+    <t>Ordenado por DEPARTAMENTO → SEXO → NOMBRE (A a Z).</t>
+  </si>
+  <si>
+    <t>3.8.4 · Filtro de departamentos</t>
+  </si>
+  <si>
+    <t>Solo Comercio y Marketing; los demás departamentos se excluyen de esta vista.</t>
+  </si>
+  <si>
+    <t>3.8.5 · Buscar y reemplazar</t>
+  </si>
+  <si>
+    <t>Todas las comisiones del 15 % se han sustituido por 13 % (3 coincidencias).</t>
+  </si>
+  <si>
+    <t>&gt;=5</t>
+  </si>
+  <si>
+    <t>Alondra Gómez - Femenino</t>
+  </si>
+  <si>
+    <t>Mujer</t>
+  </si>
+  <si>
+    <t>&gt;30</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
+  </numFmts>
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF17365D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F0FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -196,19 +358,28 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{F7FDC4E9-A54D-42AA-BB19-F15711D54563}"/>
+    <cellStyle name="Porcentaje" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -266,108 +437,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -379,23 +456,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
                 <a:lumMod val="110000"/>
                 <a:satMod val="105000"/>
-                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="103000"/>
-                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="109000"/>
-                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -405,23 +482,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
                 <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
                 <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
                 <a:lumMod val="99000"/>
                 <a:satMod val="120000"/>
-                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -429,26 +506,23 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -483,17 +557,17 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -508,70 +582,45 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57BAF7F3-0FC9-47E2-8C6C-59D172049582}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="10" width="14.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
     </row>
@@ -580,24 +629,24 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E2">
         <v>23</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="3">
         <v>0.06</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="4">
         <v>23660</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="1">
         <v>43466</v>
       </c>
     </row>
@@ -606,24 +655,24 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E3">
         <v>53</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="3">
         <v>0.1</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="4">
         <v>19540</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="1">
         <v>43831</v>
       </c>
     </row>
@@ -632,24 +681,24 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E4">
         <v>23</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="3">
         <v>0.15</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="4">
         <v>18904</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="1">
         <v>44197</v>
       </c>
     </row>
@@ -658,24 +707,24 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E5">
         <v>35</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="3">
         <v>0.05</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="4">
         <v>17980</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="1">
         <v>44562</v>
       </c>
     </row>
@@ -684,24 +733,24 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E6">
         <v>43</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="3">
         <v>0.05</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="4">
         <v>23980</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="1">
         <v>44927</v>
       </c>
     </row>
@@ -713,21 +762,21 @@
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E7">
         <v>27</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="3">
         <v>0.15</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="4">
         <v>23421</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="1">
         <v>45292</v>
       </c>
     </row>
@@ -736,24 +785,24 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E8">
         <v>38</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="3">
         <v>0.1</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="4">
         <v>18322</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="1">
         <v>45658</v>
       </c>
     </row>
@@ -762,24 +811,24 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E9">
         <v>49</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="3">
         <v>0.1</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="4">
         <v>231500</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="1">
         <v>46023</v>
       </c>
     </row>
@@ -788,24 +837,24 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E10">
         <v>28</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="3">
         <v>0.15</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="4">
         <v>23043</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="1">
         <v>46388</v>
       </c>
     </row>
@@ -814,10 +863,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D11" t="s">
         <v>25</v>
@@ -825,31 +874,28 @@
       <c r="E11">
         <v>35</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="3">
         <v>0.05</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="4">
         <v>16483</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="1">
         <v>46753</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I11">
-    <sortCondition ref="A3:A11"/>
-  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66ACEB54-C671-44D2-AA26-55B5DD192F8B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="13" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -895,7 +941,7 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <v>18500</v>
@@ -936,7 +982,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <v>21309</v>
@@ -977,7 +1023,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B4">
         <v>21568</v>
@@ -1018,7 +1064,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B5">
         <v>24377</v>
@@ -1059,7 +1105,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B6">
         <v>24636</v>
@@ -1141,7 +1187,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B8">
         <v>27704</v>
@@ -1182,7 +1228,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B9">
         <v>27963</v>
@@ -1223,7 +1269,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B10">
         <v>30772</v>
@@ -1264,7 +1310,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B11">
         <v>20031</v>
@@ -1306,4 +1352,1619 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="23" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="5" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="14" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="30.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+    </row>
+    <row r="2" spans="1:9" ht="27.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="23" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="5" max="14" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="30.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+    </row>
+    <row r="2" spans="1:9" ht="27.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="23" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="5" max="14" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="30.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+    </row>
+    <row r="2" spans="1:9" ht="27.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED41D36-5717-4634-AFBA-D32F52740757}">
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="10" width="14.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2">
+        <v>23</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0.06</v>
+      </c>
+      <c r="G2" s="4">
+        <v>23660</v>
+      </c>
+      <c r="H2" s="1">
+        <v>43466</v>
+      </c>
+      <c r="I2" t="str">
+        <f t="shared" ref="I2:I11" si="0">B2&amp;" - "&amp;C2</f>
+        <v>Alma Gutiérrez - Femenino</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3">
+        <v>23</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="G3" s="4">
+        <v>18904</v>
+      </c>
+      <c r="H3" s="1">
+        <v>44197</v>
+      </c>
+      <c r="I3" t="str">
+        <f t="shared" si="0"/>
+        <v>Miguel Ladrón - Masculino</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4">
+        <v>27</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="G4" s="4">
+        <v>23421</v>
+      </c>
+      <c r="H4" s="1">
+        <v>45292</v>
+      </c>
+      <c r="I4" t="str">
+        <f t="shared" si="0"/>
+        <v>Rosaura Yépez - Femenino</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5">
+        <v>28</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="G5" s="4">
+        <v>23043</v>
+      </c>
+      <c r="H5" s="1">
+        <v>46388</v>
+      </c>
+      <c r="I5" t="str">
+        <f t="shared" si="0"/>
+        <v>Gilberto Galardi - Femenino</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6">
+        <v>35</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="G6" s="4">
+        <v>17980</v>
+      </c>
+      <c r="H6" s="1">
+        <v>44562</v>
+      </c>
+      <c r="I6" t="str">
+        <f t="shared" si="0"/>
+        <v>Cecilia Jaca - Femenino</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7">
+        <v>35</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="G7" s="4">
+        <v>16483</v>
+      </c>
+      <c r="H7" s="1">
+        <v>46753</v>
+      </c>
+      <c r="I7" t="str">
+        <f t="shared" si="0"/>
+        <v>Víctor Yépez - Masculino</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8">
+        <v>38</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="G8" s="4">
+        <v>18322</v>
+      </c>
+      <c r="H8" s="1">
+        <v>45658</v>
+      </c>
+      <c r="I8" t="str">
+        <f t="shared" si="0"/>
+        <v>Alondra Gómez - Femenino</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9">
+        <v>43</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="G9" s="4">
+        <v>23980</v>
+      </c>
+      <c r="H9" s="1">
+        <v>44927</v>
+      </c>
+      <c r="I9" t="str">
+        <f t="shared" si="0"/>
+        <v>Alejandro Gómez - Masculino</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10">
+        <v>49</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="G10" s="4">
+        <v>231500</v>
+      </c>
+      <c r="H10" s="1">
+        <v>46023</v>
+      </c>
+      <c r="I10" t="str">
+        <f t="shared" si="0"/>
+        <v>Argenee Alamo - Femenino</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11">
+        <v>53</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="G11" s="4">
+        <v>19540</v>
+      </c>
+      <c r="H11" s="1">
+        <v>43831</v>
+      </c>
+      <c r="I11" t="str">
+        <f t="shared" si="0"/>
+        <v>Israel Fonseca - Masculino</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A6C81B-9D68-4705-96B6-507C74663D37}">
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="8" width="14.5546875" customWidth="1"/>
+    <col min="9" max="9" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2">
+        <v>23</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0.06</v>
+      </c>
+      <c r="G2" s="4">
+        <v>23660</v>
+      </c>
+      <c r="H2" s="1">
+        <v>43466</v>
+      </c>
+      <c r="I2" t="str">
+        <f t="shared" ref="I2:I11" si="0">B2&amp;" - "&amp;C2</f>
+        <v>Alma Gutiérrez - Mujer</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3">
+        <v>53</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="G3" s="4">
+        <v>19540</v>
+      </c>
+      <c r="H3" s="1">
+        <v>43831</v>
+      </c>
+      <c r="I3" t="str">
+        <f t="shared" si="0"/>
+        <v>Israel Fonseca - Masculino</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4">
+        <v>23</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="G4" s="4">
+        <v>18904</v>
+      </c>
+      <c r="H4" s="1">
+        <v>44197</v>
+      </c>
+      <c r="I4" t="str">
+        <f t="shared" si="0"/>
+        <v>Miguel Ladrón - Masculino</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5">
+        <v>35</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="G5" s="4">
+        <v>17980</v>
+      </c>
+      <c r="H5" s="1">
+        <v>44562</v>
+      </c>
+      <c r="I5" t="str">
+        <f t="shared" si="0"/>
+        <v>Cecilia Jaca - Mujer</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6">
+        <v>43</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="G6" s="4">
+        <v>23980</v>
+      </c>
+      <c r="H6" s="1">
+        <v>44927</v>
+      </c>
+      <c r="I6" t="str">
+        <f t="shared" si="0"/>
+        <v>Alejandro Gómez - Masculino</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7">
+        <v>27</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="G7" s="4">
+        <v>23421</v>
+      </c>
+      <c r="H7" s="1">
+        <v>45292</v>
+      </c>
+      <c r="I7" t="str">
+        <f t="shared" si="0"/>
+        <v>Rosaura Yépez - Mujer</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8">
+        <v>38</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="G8" s="4">
+        <v>18322</v>
+      </c>
+      <c r="H8" s="1">
+        <v>45658</v>
+      </c>
+      <c r="I8" t="str">
+        <f t="shared" si="0"/>
+        <v>Alondra Gómez - Mujer</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9">
+        <v>49</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="G9" s="4">
+        <v>231500</v>
+      </c>
+      <c r="H9" s="1">
+        <v>46023</v>
+      </c>
+      <c r="I9" t="str">
+        <f t="shared" si="0"/>
+        <v>Argenee Alamo - Mujer</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10">
+        <v>28</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="G10" s="4">
+        <v>23043</v>
+      </c>
+      <c r="H10" s="1">
+        <v>46388</v>
+      </c>
+      <c r="I10" t="str">
+        <f t="shared" si="0"/>
+        <v>Gilberto Galardi - Mujer</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11">
+        <v>35</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="G11" s="4">
+        <v>16483</v>
+      </c>
+      <c r="H11" s="1">
+        <v>46753</v>
+      </c>
+      <c r="I11" t="str">
+        <f t="shared" si="0"/>
+        <v>Víctor Yépez - Masculino</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D66F3A6-CAD8-4C8F-A687-704B21E858B4}">
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="8" width="14.5546875" customWidth="1"/>
+    <col min="9" max="9" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2">
+        <v>23</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0.06</v>
+      </c>
+      <c r="G2" s="4">
+        <v>23660</v>
+      </c>
+      <c r="H2" s="1">
+        <v>43466</v>
+      </c>
+      <c r="I2" t="str">
+        <f t="shared" ref="I2:I11" si="0">B2&amp;" - "&amp;C2</f>
+        <v>Alma Gutiérrez - Femenino</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3">
+        <v>53</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="G3" s="4">
+        <v>19540</v>
+      </c>
+      <c r="H3" s="1">
+        <v>43831</v>
+      </c>
+      <c r="I3" t="str">
+        <f t="shared" si="0"/>
+        <v>Israel Fonseca - Masculino</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4">
+        <v>23</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="G4" s="4">
+        <v>18904</v>
+      </c>
+      <c r="H4" s="1">
+        <v>44197</v>
+      </c>
+      <c r="I4" t="str">
+        <f t="shared" si="0"/>
+        <v>Miguel Ladrón - Masculino</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5">
+        <v>35</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="G5" s="4">
+        <v>17980</v>
+      </c>
+      <c r="H5" s="1">
+        <v>44562</v>
+      </c>
+      <c r="I5" t="str">
+        <f t="shared" si="0"/>
+        <v>Cecilia Jaca - Femenino</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6">
+        <v>43</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="G6" s="4">
+        <v>23980</v>
+      </c>
+      <c r="H6" s="1">
+        <v>44927</v>
+      </c>
+      <c r="I6" t="str">
+        <f t="shared" si="0"/>
+        <v>Alejandro Gómez - Masculino</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7">
+        <v>27</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="G7" s="4">
+        <v>23421</v>
+      </c>
+      <c r="H7" s="1">
+        <v>45292</v>
+      </c>
+      <c r="I7" t="str">
+        <f t="shared" si="0"/>
+        <v>Rosaura Yépez - Femenino</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8">
+        <v>38</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="G8" s="4">
+        <v>18322</v>
+      </c>
+      <c r="H8" s="1">
+        <v>45658</v>
+      </c>
+      <c r="I8" t="str">
+        <f t="shared" si="0"/>
+        <v>Alondra Gómez - Femenino</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9">
+        <v>49</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="G9" s="4">
+        <v>231500</v>
+      </c>
+      <c r="H9" s="1">
+        <v>46023</v>
+      </c>
+      <c r="I9" t="str">
+        <f t="shared" si="0"/>
+        <v>Argenee Alamo - Femenino</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10">
+        <v>28</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="G10" s="4">
+        <v>23043</v>
+      </c>
+      <c r="H10" s="1">
+        <v>46388</v>
+      </c>
+      <c r="I10" t="str">
+        <f t="shared" si="0"/>
+        <v>Gilberto Galardi - Femenino</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11">
+        <v>35</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="G11" s="4">
+        <v>16483</v>
+      </c>
+      <c r="H11" s="1">
+        <v>46753</v>
+      </c>
+      <c r="I11" t="str">
+        <f t="shared" si="0"/>
+        <v>Víctor Yépez - Masculino</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75D70E13-2E29-4D23-BDA1-21E10CD20CE3}">
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="10" width="14.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2">
+        <v>23</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0.06</v>
+      </c>
+      <c r="G2" s="4">
+        <v>23660</v>
+      </c>
+      <c r="H2" s="1">
+        <v>43466</v>
+      </c>
+      <c r="I2" t="str">
+        <f t="shared" ref="I2:I11" si="0">B2&amp;" - "&amp;C2</f>
+        <v>Alma Gutiérrez - Femenino</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3">
+        <v>35</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="G3" s="4">
+        <v>17980</v>
+      </c>
+      <c r="H3" s="1">
+        <v>44562</v>
+      </c>
+      <c r="I3" t="str">
+        <f t="shared" si="0"/>
+        <v>Cecilia Jaca - Femenino</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4">
+        <v>27</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="G4" s="4">
+        <v>23421</v>
+      </c>
+      <c r="H4" s="1">
+        <v>45292</v>
+      </c>
+      <c r="I4" t="str">
+        <f t="shared" si="0"/>
+        <v>Rosaura Yépez - Femenino</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5">
+        <v>38</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="G5" s="4">
+        <v>18322</v>
+      </c>
+      <c r="H5" s="1">
+        <v>45658</v>
+      </c>
+      <c r="I5" t="str">
+        <f t="shared" si="0"/>
+        <v>Alondra Gómez - Femenino</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6">
+        <v>49</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="G6" s="4">
+        <v>231500</v>
+      </c>
+      <c r="H6" s="1">
+        <v>46023</v>
+      </c>
+      <c r="I6" t="str">
+        <f t="shared" si="0"/>
+        <v>Argenee Alamo - Femenino</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7">
+        <v>28</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="G7" s="4">
+        <v>23043</v>
+      </c>
+      <c r="H7" s="1">
+        <v>46388</v>
+      </c>
+      <c r="I7" t="str">
+        <f t="shared" si="0"/>
+        <v>Gilberto Galardi - Femenino</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8">
+        <v>53</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="G8" s="4">
+        <v>19540</v>
+      </c>
+      <c r="H8" s="1">
+        <v>43831</v>
+      </c>
+      <c r="I8" t="str">
+        <f t="shared" si="0"/>
+        <v>Israel Fonseca - Masculino</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9">
+        <v>23</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="G9" s="4">
+        <v>18904</v>
+      </c>
+      <c r="H9" s="1">
+        <v>44197</v>
+      </c>
+      <c r="I9" t="str">
+        <f t="shared" si="0"/>
+        <v>Miguel Ladrón - Masculino</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10">
+        <v>43</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="G10" s="4">
+        <v>23980</v>
+      </c>
+      <c r="H10" s="1">
+        <v>44927</v>
+      </c>
+      <c r="I10" t="str">
+        <f t="shared" si="0"/>
+        <v>Alejandro Gómez - Masculino</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11">
+        <v>35</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="G11" s="4">
+        <v>16483</v>
+      </c>
+      <c r="H11" s="1">
+        <v>46753</v>
+      </c>
+      <c r="I11" t="str">
+        <f t="shared" si="0"/>
+        <v>Víctor Yépez - Masculino</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C14" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>7</v>
+      </c>
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17">
+        <v>38</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="G17" s="4">
+        <v>18322</v>
+      </c>
+      <c r="H17" s="1">
+        <v>45658</v>
+      </c>
+      <c r="I17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I11">
+    <sortCondition ref="C3:C11"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>